--- a/data/trans_bre/P16A04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,79</t>
+          <t>-0,6; 1,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,16</t>
+          <t>-2,78; 1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,95</t>
+          <t>-1,19; 1,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,79</t>
+          <t>-1,15; 1,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 326,11</t>
+          <t>-45,74; 324,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,68; 49,91</t>
+          <t>-57,74; 63,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 192,3</t>
+          <t>-48,29; 184,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,26; 162,7</t>
+          <t>-41,12; 122,47</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,64</t>
+          <t>-2,29; 0,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,99</t>
+          <t>-0,76; 2,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,62</t>
+          <t>-0,92; 1,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,82</t>
+          <t>-0,15; 2,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,2; 38,42</t>
+          <t>-64,24; 40,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 131,44</t>
+          <t>-18,64; 137,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 134,67</t>
+          <t>-38,07; 122,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 289,62</t>
+          <t>-7,55; 281,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,06</t>
+          <t>0,86; 4,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,29</t>
+          <t>-3,01; 0,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,96</t>
+          <t>-0,68; 2,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,54</t>
+          <t>-2,18; 1,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,67; 514,22</t>
+          <t>31,29; 526,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-77,94; 24,35</t>
+          <t>-78,63; 12,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 255,74</t>
+          <t>-43,7; 302,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 92,01</t>
+          <t>-61,53; 99,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,18</t>
+          <t>-1,02; 1,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,96</t>
+          <t>-0,72; 1,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,17</t>
+          <t>-1,77; 1,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,48</t>
+          <t>-0,19; 3,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 94,14</t>
+          <t>-42,84; 114,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 157,73</t>
+          <t>-29,5; 138,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 53,24</t>
+          <t>-48,77; 61,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 181,32</t>
+          <t>-7,71; 180,47</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,2</t>
+          <t>-0,25; 1,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,88</t>
+          <t>-0,91; 0,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,98</t>
+          <t>-0,45; 1,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,81</t>
+          <t>0,11; 1,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 80,16</t>
+          <t>-12,04; 76,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 37,74</t>
+          <t>-27,9; 35,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 55,63</t>
+          <t>-19,66; 59,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 106,98</t>
+          <t>4,36; 107,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,91</t>
+          <t>-0,57; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,37</t>
+          <t>-2,9; 1,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,94</t>
+          <t>-1,27; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,58</t>
+          <t>-1,24; 1,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 324,45</t>
+          <t>-43,47; 308,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 63,25</t>
+          <t>-58,31; 50,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,29; 184,02</t>
+          <t>-50,01; 182,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,12; 122,47</t>
+          <t>-43,46; 129,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,65</t>
+          <t>-2,03; 0,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,9</t>
+          <t>-0,75; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,68</t>
+          <t>-1,01; 1,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,79</t>
+          <t>-0,61; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 40,79</t>
+          <t>-61,62; 47,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 137,13</t>
+          <t>-21,34; 125,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 122,5</t>
+          <t>-39,79; 116,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 281,92</t>
+          <t>-22,91; 132,33</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,7%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,08</t>
+          <t>0,75; 4,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,13</t>
+          <t>-2,83; 0,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,06</t>
+          <t>-0,74; 2,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,62</t>
+          <t>-0,84; 2,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,29; 526,91</t>
+          <t>18,44; 523,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,63; 12,53</t>
+          <t>-77,27; 18,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,7; 302,17</t>
+          <t>-44,73; 305,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 99,32</t>
+          <t>-26,87; 166,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,32</t>
+          <t>-1,14; 1,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,83</t>
+          <t>-0,71; 2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,29</t>
+          <t>-1,76; 1,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,46</t>
+          <t>0,22; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 114,7</t>
+          <t>-48,81; 100,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 138,06</t>
+          <t>-28,62; 162,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,77; 61,24</t>
+          <t>-48,75; 61,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 180,47</t>
+          <t>3,28; 171,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,1</t>
+          <t>-0,29; 1,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,86</t>
+          <t>-0,86; 0,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,01</t>
+          <t>-0,47; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,82</t>
+          <t>0,23; 1,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 76,57</t>
+          <t>-14,59; 76,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,9; 35,43</t>
+          <t>-24,93; 39,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 59,52</t>
+          <t>-20,1; 58,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 107,77</t>
+          <t>7,87; 88,51</t>
         </is>
       </c>
     </row>
